--- a/results/result1.xlsx
+++ b/results/result1.xlsx
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>0.003542477898717326</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" ht="14" customHeight="1">
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="B71" s="7" t="n">
-        <v>179.2727979696778</v>
+        <v>179.2771713991827</v>
       </c>
     </row>
     <row r="72" ht="14" customHeight="1">
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="B141" s="7" t="n">
-        <v>569.3586333333333</v>
+        <v>902.6919666666665</v>
       </c>
     </row>
     <row r="142" ht="14" customHeight="1">
@@ -1884,7 +1884,7 @@
         </is>
       </c>
       <c r="B143" s="7" t="n">
-        <v>904.9487166666667</v>
+        <v>571.6153833333333</v>
       </c>
     </row>
     <row r="144" ht="14" customHeight="1">
@@ -1984,7 +1984,7 @@
         <v>833.3333333333333</v>
       </c>
       <c r="C3" t="n">
-        <v>6365.837657522101</v>
+        <v>6365.8412</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4787.959914636343</v>
+        <v>4787.964288065848</v>
       </c>
       <c r="C4" t="n">
         <v>1702.996983333333</v>
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5333.333333333332</v>
+        <v>5333.333333333333</v>
       </c>
       <c r="C7" t="n">
         <v>2859.868116666667</v>
